--- a/public/exports-60-250-with-coowners/19438414.xlsx
+++ b/public/exports-60-250-with-coowners/19438414.xlsx
@@ -4339,7 +4339,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6079,12 +6079,12 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
